--- a/master_cybercrime_intelligence_india_2020_2026.xlsx
+++ b/master_cybercrime_intelligence_india_2020_2026.xlsx
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>INDIA CYBERCRIME INTELLIGENCE INITIATIVE (2020–2026 YTD)</t>
+          <t>CYBER JAGRUTI — INDIA CYBERCRIME INTELLIGENCE INITIATIVE (2020–2026 YTD)</t>
         </is>
       </c>
     </row>
